--- a/outputs/43657.xlsx
+++ b/outputs/43657.xlsx
@@ -230,67 +230,67 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/outputs/43657.xlsx
+++ b/outputs/43657.xlsx
@@ -607,8 +607,8 @@
         <v>44387</v>
       </c>
       <c r="K2" s="6" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L2,C3:G3)))+SUMPRODUCT(--ISNUMBER(SEARCH(L2,C10:G10)))+SUMPRODUCT(--ISNUMBER(SEARCH(L2,C17:G17)))+SUMPRODUCT(--ISNUMBER(SEARCH(L2,C24:G24)))</f>
-        <v>3</v>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L2,C3:G3)))</f>
+        <v>2</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>7</v>
@@ -635,8 +635,8 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="K3" s="6" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L3,C3:G3)))+SUMPRODUCT(--ISNUMBER(SEARCH(L3,C10:G10)))+SUMPRODUCT(--ISNUMBER(SEARCH(L3,C17:G17)))+SUMPRODUCT(--ISNUMBER(SEARCH(L3,C24:G24)))</f>
-        <v>5</v>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L3,C3:G3)))</f>
+        <v>1</v>
       </c>
       <c r="L3" s="11" t="s">
         <v>12</v>
@@ -653,8 +653,8 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="K4" s="6" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L4,C3:G3)))+SUMPRODUCT(--ISNUMBER(SEARCH(L4,C10:G10)))+SUMPRODUCT(--ISNUMBER(SEARCH(L4,C17:G17)))+SUMPRODUCT(--ISNUMBER(SEARCH(L4,C24:G24)))</f>
-        <v>3</v>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L4,C3:G3)))</f>
+        <v>1</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>10</v>
@@ -671,8 +671,8 @@
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="K5" s="6" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L5,C3:G3)))+SUMPRODUCT(--ISNUMBER(SEARCH(L5,C10:G10)))+SUMPRODUCT(--ISNUMBER(SEARCH(L5,C17:G17)))+SUMPRODUCT(--ISNUMBER(SEARCH(L5,C24:G24)))</f>
-        <v>2</v>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L5,C3:G3)))</f>
+        <v>0</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>13</v>
@@ -689,8 +689,8 @@
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="K6" s="6" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L6,C3:G3)))+SUMPRODUCT(--ISNUMBER(SEARCH(L6,C10:G10)))+SUMPRODUCT(--ISNUMBER(SEARCH(L6,C17:G17)))+SUMPRODUCT(--ISNUMBER(SEARCH(L6,C24:G24)))</f>
-        <v>2</v>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L6,C3:G3)))</f>
+        <v>1</v>
       </c>
       <c r="L6" s="11" t="s">
         <v>14</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K7" s="6" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L7,C3:G3)))+SUMPRODUCT(--ISNUMBER(SEARCH(L7,C10:G10)))+SUMPRODUCT(--ISNUMBER(SEARCH(L7,C17:G17)))+SUMPRODUCT(--ISNUMBER(SEARCH(L7,C24:G24)))</f>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L7,C3:G3)))</f>
         <v>0</v>
       </c>
       <c r="L7" s="6" t="s">
@@ -728,8 +728,8 @@
         <v>6</v>
       </c>
       <c r="K8" s="6" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L8,C3:G3)))+SUMPRODUCT(--ISNUMBER(SEARCH(L8,C10:G10)))+SUMPRODUCT(--ISNUMBER(SEARCH(L8,C17:G17)))+SUMPRODUCT(--ISNUMBER(SEARCH(L8,C24:G24)))</f>
-        <v>3</v>
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(L8,C3:G3)))</f>
+        <v>1</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>16</v>
